--- a/samples/factura_honorarios.xlsx
+++ b/samples/factura_honorarios.xlsx
@@ -432,7 +432,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIT: 860.998.331-7</t>
+          <t>NIT: 860.998.331-6</t>
         </is>
       </c>
     </row>
